--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -160,16 +160,16 @@
     <t>天命</t>
   </si>
   <si>
-    <t>30022,30024,30026,30028,30030</t>
-  </si>
-  <si>
-    <t>10000,1000,100,10,50</t>
-  </si>
-  <si>
-    <t>100,10,1,0.1,-0.5</t>
-  </si>
-  <si>
-    <t>最终伤害有0.1%提高{0}%，1%提高{1}%，10%提高{2}%，40%提高{3}%，48.9%降低{4}%</t>
+    <t>30022,30024,30026,30028</t>
+  </si>
+  <si>
+    <t>1000,100,10,1</t>
+  </si>
+  <si>
+    <t>10,1,0.1,0.1</t>
+  </si>
+  <si>
+    <t>最终伤害有0.1%提高{0}%，1%提高{1}%，10%提高{2}%，40%提高{3}%，48.9%无变化</t>
   </si>
   <si>
     <t>福运</t>

--- a/Excel/EquipLegendSetConfig.xlsx
+++ b/Excel/EquipLegendSetConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="70">
   <si>
     <t>_Id</t>
   </si>
@@ -212,6 +212,36 @@
   </si>
   <si>
     <t>敌人生命低于{0}%的时候，直接斩杀敌人</t>
+  </si>
+  <si>
+    <t>不灭</t>
+  </si>
+  <si>
+    <t>10001</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>生命倍率+{0}%</t>
+  </si>
+  <si>
+    <t>镇岳</t>
+  </si>
+  <si>
+    <t>10002</t>
+  </si>
+  <si>
+    <t>防御倍率+{0}%</t>
+  </si>
+  <si>
+    <t>冰霜</t>
+  </si>
+  <si>
+    <t>10028</t>
+  </si>
+  <si>
+    <t>减伤倍率+{0}%</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1208,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:I17"/>
+  <dimension ref="C3:I20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1535,6 +1565,75 @@
         <v>59</v>
       </c>
     </row>
+    <row r="18" customHeight="1" spans="3:9">
+      <c r="C18" s="1">
+        <v>13</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:9">
+      <c r="C19" s="1">
+        <v>14</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E19" s="1">
+        <v>3</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:9">
+      <c r="C20" s="1">
+        <v>15</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="1">
+        <v>3</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5" errorStyle="warning">
